--- a/Research Logs/Matt/Matt Baker - Week 11 Research Log.xlsx
+++ b/Research Logs/Matt/Matt Baker - Week 11 Research Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RecoveryAdmin\Documents\BHB-Capstone\Research Logs\Matt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15EB4DB5-3AA5-4D43-AE82-E6FB440FC4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D317E455-628C-4F97-8B2C-B152E2E20BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10455" yWindow="0" windowWidth="22635" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="154">
   <si>
     <t>Date</t>
   </si>
@@ -571,6 +571,19 @@
   <si>
     <t>Learned about langchain, RAG, vectors, embedding models, pandas, chroma database.
 Helped me in attempting to create POC code that efficiently retrieves data from embedded/vectorised nmap scans.</t>
+  </si>
+  <si>
+    <t>Finding alternatives to the linux 'top' command, general learning about 'top' and other 
+system monitoring tools</t>
+  </si>
+  <si>
+    <t>Google
+https://itsfoss.com/linux-system-monitoring-tools/
+manual pages of tools via linux command: "man {tool_name}"</t>
+  </si>
+  <si>
+    <t>Learned about different options and utitlities that can be 
+expected/may be useful for our performance recording. nvtop and htop are the best for us. Gives us a good range of gpu, cpu, memory resource usage when used together. Both are by different developers but have pretty much the same UI.</t>
   </si>
 </sst>
 </file>
@@ -942,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G65"/>
+  <dimension ref="B2:G67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" style="3" customWidth="1"/>
@@ -959,7 +972,7 @@
       </c>
       <c r="D2" s="5">
         <f>ROUNDDOWN(SUM(C6:C499)/60,0)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -971,7 +984,7 @@
       </c>
       <c r="D3" s="5">
         <f>ROUND(MOD(SUM(C6:C499),60),0)</f>
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -1884,6 +1897,29 @@
       <c r="G65" s="2" t="s">
         <v>149</v>
       </c>
+    </row>
+    <row r="66" spans="2:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="B66" s="3">
+        <v>46287</v>
+      </c>
+      <c r="C66">
+        <v>30</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G67" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Research Logs/Matt/Matt Baker - Week 11 Research Log.xlsx
+++ b/Research Logs/Matt/Matt Baker - Week 11 Research Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RecoveryAdmin\Documents\BHB-Capstone\Research Logs\Matt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D317E455-628C-4F97-8B2C-B152E2E20BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F30031A-7ECC-4279-8672-F235FA8689EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10455" yWindow="0" windowWidth="22635" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="870" windowWidth="37770" windowHeight="17970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="157">
   <si>
     <t>Date</t>
   </si>
@@ -555,10 +555,6 @@
     <t>Week 11</t>
   </si>
   <si>
-    <t>Learn the Ollama python library, I belive this means I wont have to run scripts directly through
-command line with subprocess anymore</t>
-  </si>
-  <si>
     <t>Wanting to learn and experiment with creating a RAG AI agent with ollama and python. 
 Also wanting to learn about Retrieval Augmented Generation (RAG) itself and how to impliement it</t>
   </si>
@@ -584,6 +580,21 @@
   <si>
     <t>Learned about different options and utitlities that can be 
 expected/may be useful for our performance recording. nvtop and htop are the best for us. Gives us a good range of gpu, cpu, memory resource usage when used together. Both are by different developers but have pretty much the same UI.</t>
+  </si>
+  <si>
+    <t>Searching/Watching/Reading</t>
+  </si>
+  <si>
+    <t>Looking for how to efficiently feed JSON/alternative data to Ollama</t>
+  </si>
+  <si>
+    <t>Learned about "Tokenizer playground" - lets me
+calculate token cost from prompt type to see how much I waste.</t>
+  </si>
+  <si>
+    <t>Google, Youtube
+https://www.youtube.com/watch?v=nhsJ34jPyYI
+https://huggingface.co/spaces/Xenova/the-tokenizer-playground</t>
   </si>
 </sst>
 </file>
@@ -959,7 +970,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" style="3" customWidth="1"/>
-    <col min="3" max="4" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
     <col min="5" max="5" width="91.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="54.5703125" customWidth="1"/>
     <col min="7" max="7" width="131" customWidth="1"/>
@@ -984,7 +996,7 @@
       </c>
       <c r="D3" s="5">
         <f>ROUND(MOD(SUM(C6:C499),60),0)</f>
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -1870,52 +1882,64 @@
         <v>145</v>
       </c>
     </row>
-    <row r="64" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:7" ht="75" x14ac:dyDescent="0.25">
       <c r="B64" s="3">
         <v>46286</v>
       </c>
+      <c r="C64">
+        <v>30</v>
+      </c>
+      <c r="D64" t="s">
+        <v>147</v>
+      </c>
       <c r="E64" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="65" spans="2:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="F64" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="90" x14ac:dyDescent="0.25">
       <c r="B65" s="3">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C65">
         <v>30</v>
       </c>
       <c r="D65" t="s">
-        <v>148</v>
+        <v>12</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="66" spans="2:7" ht="90" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" ht="45" x14ac:dyDescent="0.25">
       <c r="B66" s="3">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C66">
         <v>30</v>
       </c>
       <c r="D66" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
+      </c>
+      <c r="E66" t="s">
+        <v>154</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.25">
@@ -1943,7 +1967,8 @@
     <hyperlink ref="G58" r:id="rId18" display="https://github.com/D4-project/nmap2json" xr:uid="{C857808A-F7DD-4DA4-B603-3F21024AF8C8}"/>
     <hyperlink ref="G59" r:id="rId19" display="https://stackoverflow.com/questions/4703390/how-to-extract-a-floating-number-from-a-string" xr:uid="{42FBAB5B-B3FE-4D89-B36B-858373BD4E7F}"/>
     <hyperlink ref="G60" r:id="rId20" display="https://stackoverflow.com/questions/7764755/how-to-split-a-file-into-equal-parts-without-breaking-individual-lines" xr:uid="{615EDF51-691E-4C89-9084-02AF4FF3F8C0}"/>
-    <hyperlink ref="G65" r:id="rId21" xr:uid="{2E2E53C3-9E40-4EB6-B3BD-4CE74D1603C9}"/>
+    <hyperlink ref="G64" r:id="rId21" xr:uid="{2E2E53C3-9E40-4EB6-B3BD-4CE74D1603C9}"/>
+    <hyperlink ref="G66" r:id="rId22" display="https://www.youtube.com/watch?v=nhsJ34jPyYI" xr:uid="{E83DCEEE-B1DD-4F61-8945-68D9770C1B51}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Research Logs/Matt/Matt Baker - Week 11 Research Log.xlsx
+++ b/Research Logs/Matt/Matt Baker - Week 11 Research Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RecoveryAdmin\Documents\BHB-Capstone\Research Logs\Matt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F30031A-7ECC-4279-8672-F235FA8689EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0703CCD-ABB4-404F-82E7-9F0CEC0E81F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="870" windowWidth="37770" windowHeight="17970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="37770" windowHeight="17970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="165">
   <si>
     <t>Date</t>
   </si>
@@ -582,19 +582,46 @@
 expected/may be useful for our performance recording. nvtop and htop are the best for us. Gives us a good range of gpu, cpu, memory resource usage when used together. Both are by different developers but have pretty much the same UI.</t>
   </si>
   <si>
-    <t>Searching/Watching/Reading</t>
-  </si>
-  <si>
     <t>Looking for how to efficiently feed JSON/alternative data to Ollama</t>
-  </si>
-  <si>
-    <t>Learned about "Tokenizer playground" - lets me
-calculate token cost from prompt type to see how much I waste.</t>
   </si>
   <si>
     <t>Google, Youtube
 https://www.youtube.com/watch?v=nhsJ34jPyYI
 https://huggingface.co/spaces/Xenova/the-tokenizer-playground</t>
+  </si>
+  <si>
+    <t>Learned about "Tokenizer playground" - lets me
+calculate token cost from prompt type to see how much I waste. Learned about "Token-Oriented Object Notation (TOON) which removes the token-increasing brackets and such from JSON format to reduce context length and token usage.</t>
+  </si>
+  <si>
+    <t>How to take advantage of the TOON format</t>
+  </si>
+  <si>
+    <t>https://github.com/toon-format/toon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The documentation </t>
+  </si>
+  <si>
+    <t>Somewhat useful way of increasing the default ollama context window, I ended up increasing via override of ollama service config file.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=edsZec6WyrY&amp;t=30s</t>
+  </si>
+  <si>
+    <t>How to increase ollama default context window</t>
+  </si>
+  <si>
+    <t>https://github.com/pymupdf/pymupdf
+https://pymupdf.readthedocs.io/en/latest/installation.html
+https://github.com/docling-project/docling
+https://py-pdf.github.io/fpdf2/Tutorial.html</t>
+  </si>
+  <si>
+    <t>Looking for python modules/libraries for generating pdfs, wanting to have my script generate reports as pdf rather than raw text. Also how to use them.</t>
+  </si>
+  <si>
+    <t>Pymupdf documentation and installation guide helped me install and understand how to employ it within a python script, although it doesn’t give explicit instructions on how to "convert" text to a pdf, it gives enough info for me to figure it out and manipulate the PDFs I generate. That one had lots of support. fpdf2 and docling were other considered options, docling is more for parsing existing docs into consumable data for LLMs.</t>
   </si>
 </sst>
 </file>
@@ -966,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G67"/>
+  <dimension ref="B2:G69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" style="3" customWidth="1"/>
@@ -984,7 +1011,7 @@
       </c>
       <c r="D2" s="5">
         <f>ROUNDDOWN(SUM(C6:C499)/60,0)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1922,7 +1949,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:7" ht="90" x14ac:dyDescent="0.25">
       <c r="B66" s="3">
         <v>46288</v>
       </c>
@@ -1930,20 +1957,77 @@
         <v>30</v>
       </c>
       <c r="D66" t="s">
+        <v>147</v>
+      </c>
+      <c r="E66" t="s">
         <v>153</v>
-      </c>
-      <c r="E66" t="s">
-        <v>154</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>155</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="3">
+        <v>46288</v>
+      </c>
+      <c r="C67">
+        <v>15</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G67" s="1"/>
+      <c r="F67" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B68" s="3">
+        <v>46290</v>
+      </c>
+      <c r="C68">
+        <v>15</v>
+      </c>
+      <c r="D68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" t="s">
+        <v>161</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="B69" s="3">
+        <v>46291</v>
+      </c>
+      <c r="C69">
+        <v>30</v>
+      </c>
+      <c r="D69" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>162</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1969,6 +2053,8 @@
     <hyperlink ref="G60" r:id="rId20" display="https://stackoverflow.com/questions/7764755/how-to-split-a-file-into-equal-parts-without-breaking-individual-lines" xr:uid="{615EDF51-691E-4C89-9084-02AF4FF3F8C0}"/>
     <hyperlink ref="G64" r:id="rId21" xr:uid="{2E2E53C3-9E40-4EB6-B3BD-4CE74D1603C9}"/>
     <hyperlink ref="G66" r:id="rId22" display="https://www.youtube.com/watch?v=nhsJ34jPyYI" xr:uid="{E83DCEEE-B1DD-4F61-8945-68D9770C1B51}"/>
+    <hyperlink ref="G68" r:id="rId23" xr:uid="{E98802B5-3E06-4001-96CC-994CEA168321}"/>
+    <hyperlink ref="G69" r:id="rId24" display="https://github.com/pymupdf/pymupdf" xr:uid="{6B6F4960-3DD5-446B-A187-1606259FE4C3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
